--- a/docs/lem/files/xslope_method_slices_problem.xlsx
+++ b/docs/lem/files/xslope_method_slices_problem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADB65BB-0662-6945-AA52-37C1BEC0F95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF95A62-CDCD-1043-8CF1-1A58142141BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25100" yWindow="3220" windowWidth="34200" windowHeight="20240" activeTab="5" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="27020" yWindow="5000" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>

--- a/docs/lem/files/xslope_method_slices_problem.xlsx
+++ b/docs/lem/files/xslope_method_slices_problem.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>X</t>
   </si>
@@ -630,6 +630,37 @@
   </si>
   <si>
     <t>soil 3</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8006,7 +8037,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9451,8 +9482,8 @@
       <c r="I8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>81</v>
+      <c r="J8" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>88</v>
@@ -9473,7 +9504,7 @@
         <v>82</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>92</v>
@@ -10235,7 +10266,7 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:F50">
+  <conditionalFormatting sqref="F9:F50">
     <cfRule type="expression" dxfId="8" priority="3">
       <formula>$D9="cp"</formula>
     </cfRule>
@@ -10250,7 +10281,7 @@
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N50">
+  <conditionalFormatting sqref="N9:N50">
     <cfRule type="expression" dxfId="5" priority="6">
       <formula>$D9="cp"</formula>
     </cfRule>

--- a/docs/lem/files/xslope_method_slices_problem.xlsx
+++ b/docs/lem/files/xslope_method_slices_problem.xlsx
@@ -5351,7 +5351,23 @@
       </c>
       <c r="D10" s="48" t="inlineStr">
         <is>
-          <t>gsat</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>sat</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="44" t="inlineStr">

--- a/docs/lem/files/xslope_method_slices_problem.xlsx
+++ b/docs/lem/files/xslope_method_slices_problem.xlsx
@@ -2641,7 +2641,26 @@
       </c>
       <c r="H2" s="40" t="inlineStr">
         <is>
-          <t>qp</t>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>q</t>
+          </r>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>p</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="40" t="inlineStr">
@@ -5482,12 +5501,64 @@
       </c>
       <c r="AA10" s="46" t="inlineStr">
         <is>
-          <t>s(g)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>g</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AB10" s="46" t="inlineStr">
         <is>
-          <t>s(c)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c)</t>
+          </r>
         </is>
       </c>
       <c r="AC10" s="47" t="inlineStr">
@@ -5497,17 +5568,70 @@
       </c>
       <c r="AD10" s="46" t="inlineStr">
         <is>
-          <t>s(c/p)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(c/p)</t>
+          </r>
         </is>
       </c>
       <c r="AE10" s="46" t="inlineStr">
         <is>
-          <t>s(d)</t>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>s</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+              <scheme val="minor"/>
+            </rPr>
+            <t>(d)</t>
+          </r>
         </is>
       </c>
       <c r="AF10" s="47" t="inlineStr">
         <is>
-          <t>s(psi)</t>
+          <r>
+            <t>s(</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Aptos Narrow"/>
+            </rPr>
+            <t>psi</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color theme="0"/>
+              <rFont val="Symbol"/>
+              <charset val="2"/>
+            </rPr>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="AG10" s="23" t="inlineStr">

--- a/docs/lem/files/xslope_method_slices_problem.xlsx
+++ b/docs/lem/files/xslope_method_slices_problem.xlsx
@@ -7641,19 +7641,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="56">
+      <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>soil 1</v>
       </c>
       <c r="B6" s="57" t="n"/>
-      <c r="D6" s="56">
+      <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>soil 2</v>
       </c>
       <c r="E6" s="57" t="n"/>
-      <c r="G6" s="56">
+      <c r="G6" s="56" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>soil 3</v>
       </c>
       <c r="H6" s="57" t="n"/>
       <c r="J6" s="56">
@@ -9272,19 +9272,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58">
+      <c r="A7" s="58" t="str">
         <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>soil 1</v>
       </c>
       <c r="B7" s="57" t="n"/>
-      <c r="D7" s="58">
+      <c r="D7" s="58" t="str">
         <f>IF(OR(E5="",E5="material"),_xlfn.XLOOKUP(E6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>soil 2</v>
       </c>
       <c r="E7" s="57" t="n"/>
-      <c r="G7" s="58">
+      <c r="G7" s="58" t="str">
         <f>IF(OR(H5="",H5="material"),_xlfn.XLOOKUP(H6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>soil 3</v>
       </c>
       <c r="H7" s="57" t="n"/>
       <c r="J7" s="58">
